--- a/BENCHMARK/Benchmark_Meta_Table.xlsx
+++ b/BENCHMARK/Benchmark_Meta_Table.xlsx
@@ -486,7 +486,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -536,7 +535,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
@@ -551,7 +549,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -580,7 +577,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -1023,7 +1019,7 @@
       <c r="E11" s="7" t="inlineStr">
         <is>
           <t>벤치마크의 음향 조건.
-clean=깨끗(스튜디오/조용한 실내) / noise=잡음 합성 / far_field=원거리 마이크 / reverb=잔향 합성 / field=현장 녹음(실외 등) / phone=전화 (8kHz 류).</t>
+clean=깨끗(스튜디오/조용한 실내) / noisy=잡음 합성 / far_field=원거리 마이크 / reverb=잔향 합성 / field=현장 녹음(실외 등) / phone=전화 (8kHz 류).</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1033,7 +1029,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>clean / noise / far_field / reverb / field / phone</t>
+          <t>clean / noisy / far_field / reverb / field / phone</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1747,7 +1743,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AIHub_KorSpontSpeech_general_other</t>
+          <t>AIHub_KorSpontSpeech_general_noisy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1767,12 +1763,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>clean</t>
+          <t>noisy</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>quiet_room</t>
+          <t>quiet_room+aug</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1782,12 +1778,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>AIHub_KorSpontSpeech 에서 어려운 발화 split</t>
+          <t>위 clean 발화 + 노이즈 합성</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>noise(SNR=10dB)</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1812,7 +1808,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>KsponSpeech eval_other 상당. clean 대비 난이도 ↑</t>
+          <t>노이즈 강건성. clean 과 발화 페어 매칭 가능.</t>
         </is>
       </c>
     </row>
@@ -1824,13 +1820,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AIHub_KorSpontSpeech_general_noise</t>
+          <t>OpenSLR_SLR40_Zeroth_ko_general_clean</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AIHub_KorSpontSpeech</t>
-        </is>
+          <t>OpenSLR_SLR40_Zeroth_ko</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>457</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1844,12 +1852,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>noise</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>quiet_room+aug</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1859,12 +1867,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>위 clean 발화 + 노이즈 합성</t>
+          <t>Zeroth 원본 test split 그대로</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>noise(SNR=10dB)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1874,7 +1882,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>연구용</t>
+          <t>상용가능</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1889,7 +1897,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>노이즈 강건성. clean 과 발화 페어 매칭 가능.</t>
+          <t>Zeroth-Korean 오픈 코퍼스. 상용 라이선스 → 외부 공유/논문 가능.</t>
         </is>
       </c>
     </row>
@@ -1901,29 +1909,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OpenSLR_SLR40_Zeroth_ko_general_clean</t>
+          <t>AIHub_CounselingSpeech_counsel_phone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OpenSLR_SLR40_Zeroth_ko</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>457</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.7</v>
+          <t>AIHub_CounselingSpeech</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>call_center</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1933,7 +1929,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>clean</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1948,7 +1944,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Zeroth 원본 test split 그대로</t>
+          <t>상담 음성 (8kHz) test split</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1963,12 +1959,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>상용가능</t>
+          <t>연구용</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.2</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1978,7 +1974,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Zeroth-Korean 오픈 코퍼스. 상용 라이선스 → 외부 공유/논문 가능.</t>
+          <t>Awesome-KSR '상담 음성' 호환. 8kHz 전화 상담.</t>
         </is>
       </c>
     </row>
@@ -1990,12 +1986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AIHub_CounselingSpeech_counsel_phone</t>
+          <t>AIHub_CallcenterQA_Audio_counsel_studio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AIHub_CounselingSpeech</t>
+          <t>AIHub_CallcenterQA_Audio</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2010,12 +2006,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>studio</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2025,7 +2021,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>상담 음성 (8kHz) test split</t>
+          <t>민원 콜센터 Q&amp;A test split</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2045,7 +2041,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>v1.2</t>
+          <t>v1.3</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -2055,7 +2051,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Awesome-KSR '상담 음성' 호환. 8kHz 전화 상담.</t>
+          <t>민원 콜센터 — 가장 정제됨. studio 녹음.</t>
         </is>
       </c>
     </row>
@@ -2067,17 +2063,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AIHub_CallcenterQA_Audio_counsel_studio</t>
+          <t>AIHub_WelfareCounsel_counsel_medical</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AIHub_CallcenterQA_Audio</t>
+          <t>AIHub_WelfareCounsel</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>call_center</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2087,12 +2083,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>clean</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>studio</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2102,7 +2098,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>민원 콜센터 Q&amp;A test split</t>
+          <t>복지시설 상담 test split</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2122,7 +2118,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>v1.3</t>
+          <t>v1.0</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -2132,7 +2128,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>민원 콜센터 — 가장 정제됨. studio 녹음.</t>
+          <t>복지/의료 상담. medical 도메인 강건성.</t>
         </is>
       </c>
     </row>
@@ -2144,17 +2140,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AIHub_WelfareCounsel_counsel_medical</t>
+          <t>AIHub_LowQualityPhoneVoice_phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AIHub_WelfareCounsel</t>
+          <t>AIHub_LowQualityPhoneVoice</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>call_center</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2179,7 +2175,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>복지시설 상담 test split</t>
+          <t>저음질 전화망 test split</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2199,7 +2195,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.1</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -2209,7 +2205,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>복지/의료 상담. medical 도메인 강건성.</t>
+          <t>Awesome-KSR '저음질 전화망' 호환. 다양한 잡음.</t>
         </is>
       </c>
     </row>
@@ -2221,17 +2217,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AIHub_LowQualityPhoneVoice_phone</t>
+          <t>AIHub_KorLectureSpeech_lecture</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AIHub_LowQualityPhoneVoice</t>
+          <t>AIHub_KorLectureSpeech</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>call_center</t>
+          <t>lecture</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2241,12 +2237,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>studio</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2256,7 +2252,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>저음질 전화망 test split</t>
+          <t>한국어 강의 test split</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2276,7 +2272,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>v1.1</t>
+          <t>v1.0</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -2286,7 +2282,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Awesome-KSR '저음질 전화망' 호환. 다양한 잡음.</t>
+          <t>EBS 강의. 긴 발화 + 전문 용어. Awesome-KSR 호환.</t>
         </is>
       </c>
     </row>
@@ -2298,22 +2294,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AIHub_KorLectureSpeech_lecture</t>
+          <t>AIHub_MeetingASR_dialog</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AIHub_KorLectureSpeech</t>
+          <t>AIHub_MeetingASR</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>lecture</t>
+          <t>dialog</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2323,7 +2319,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>studio</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2333,7 +2329,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>한국어 강의 test split</t>
+          <t>회의 음성 test split (3인 이상)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2363,7 +2359,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>EBS 강의. 긴 발화 + 전문 용어. Awesome-KSR 호환.</t>
+          <t>3인 이상 회의. 자연 발화 + 발화 겹침. Awesome-KSR 호환.</t>
         </is>
       </c>
     </row>
@@ -2375,34 +2371,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AIHub_MeetingASR_dialog</t>
+          <t>AIHub_FreeDialog_Senior_elderly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AIHub_MeetingASR</t>
+          <t>AIHub_FreeDialog_Senior</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>dialog</t>
+          <t>general</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>elderly</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>clean</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>clean</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>N</t>
@@ -2410,7 +2406,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>회의 음성 test split (3인 이상)</t>
+          <t>60+ 화자 발화 샘플링 (검수 후)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2420,7 +2416,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>human-verbatim (원본)</t>
+          <t>human-review</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2430,7 +2426,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.2</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -2440,7 +2436,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>3인 이상 회의. 자연 발화 + 발화 겹침. Awesome-KSR 호환.</t>
+          <t>노인 발화 강건성. 발성/조음 변화.</t>
         </is>
       </c>
     </row>
@@ -2452,12 +2448,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AIHub_FreeDialog_Senior_elderly</t>
+          <t>AIHub_FreeDialog_Child_child</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AIHub_FreeDialog_Senior</t>
+          <t>AIHub_FreeDialog_Child</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2467,7 +2463,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>elderly</t>
+          <t>child</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2487,7 +2483,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>60+ 화자 발화 샘플링 (검수 후)</t>
+          <t>3~10세 화자 발화 샘플링</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2517,7 +2513,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>노인 발화 강건성. 발성/조음 변화.</t>
+          <t>어린이 발화 (자유대화).</t>
         </is>
       </c>
     </row>
@@ -2529,17 +2525,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AIHub_FreeDialog_Child_child</t>
+          <t>AIHub_KO_ChildSpeech_child</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AIHub_FreeDialog_Child</t>
+          <t>AIHub_KO_ChildSpeech</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2564,7 +2560,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>3~10세 화자 발화 샘플링</t>
+          <t>미취학~초등 어린이 샘플링</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2584,7 +2580,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>v1.2</t>
+          <t>v1.0</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2594,7 +2590,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>어린이 발화 (자유대화).</t>
+          <t>어린이 발화 (대안 코퍼스).</t>
         </is>
       </c>
     </row>
@@ -2606,22 +2602,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AIHub_KO_ChildSpeech_child</t>
+          <t>NIKL_Dialect_Corpus_2021_dialect</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AIHub_KO_ChildSpeech</t>
+          <t>NIKL_Dialect_Corpus_2021</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>dialect</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>elderly</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2636,12 +2632,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>미취학~초등 어린이 샘플링</t>
+          <t>강원/경상 사투리 50~80대 화자 샘플링</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2671,7 +2667,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>어린이 발화 (대안 코퍼스).</t>
+          <t>사투리 강건성. 강원/경상 + 노인.</t>
         </is>
       </c>
     </row>
@@ -2683,22 +2679,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AIHub_DialectSenior_GW_GS_dialect</t>
+          <t>AIHub_ForeignKorSpeech_foreign</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AIHub_DialectSenior_GW_GS</t>
+          <t>AIHub_ForeignKorSpeech</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>dialect</t>
+          <t>general</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>elderly</t>
+          <t>non_native</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2713,12 +2709,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>강원/경상 사투리 50~80대 화자 샘플링</t>
+          <t>비원어민 화자 샘플링</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2748,7 +2744,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>사투리 강건성. 강원/경상 + 노인.</t>
+          <t>비원어민 한국어. 다국적 화자.</t>
         </is>
       </c>
     </row>
@@ -2760,22 +2756,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AIHub_ForeignKorSpeech_foreign</t>
+          <t>AIHub_NoisyCommandSpeech_command_clean</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AIHub_ForeignKorSpeech</t>
+          <t>AIHub_NoisyCommandSpeech</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>command</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>non_native</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2785,7 +2781,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>studio</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2795,7 +2791,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>비원어민 화자 샘플링</t>
+          <t>명령 발화 clean split</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2825,7 +2821,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>비원어민 한국어. 다국적 화자.</t>
+          <t>짧은 명령 발화. hallucination 점검.</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2833,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AIHub_NoisyCommandSpeech_command_clean</t>
+          <t>AIHub_NoisyCommandSpeech_command_field</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2857,12 +2853,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>clean</t>
+          <t>field</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>studio</t>
+          <t>field</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2872,7 +2868,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>명령 발화 clean split</t>
+          <t>현장 잡음 명령 발화</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2902,7 +2898,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>짧은 명령 발화. hallucination 점검.</t>
+          <t>명령 + 현장 잡음. clean 과 페어 비교 가능.</t>
         </is>
       </c>
     </row>
@@ -2914,12 +2910,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AIHub_NoisyCommandSpeech_command_field</t>
+          <t>Internal_CafeOrder_command_clean</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AIHub_NoisyCommandSpeech</t>
+          <t>Internal_CafeOrder</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2934,12 +2930,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>field</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>field</t>
+          <t>studio</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2949,7 +2945,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>현장 잡음 명령 발화</t>
+          <t>사용자 자체 보유 카페 주문 발화</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2964,7 +2960,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>연구용</t>
+          <t>내부전용</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2979,7 +2975,12 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>명령 + 현장 잡음. clean 과 페어 비교 가능.</t>
+          <t>카페 주문 도메인. 사용자 보유 — 실제 corpus_id / 통계는 추후 갱신.</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>TODO: 통계 채우기</t>
         </is>
       </c>
     </row>
@@ -2991,17 +2992,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Internal_CafeOrder_command_clean</t>
+          <t>Sample10_general_clean</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Internal_CafeOrder</t>
-        </is>
+          <t>Sample10_PracticeRef</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>command</t>
+          <t>general</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3026,7 +3030,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>사용자 자체 보유 카페 주문 발화</t>
+          <t>/home/cssong/workspace/practice/2601_sensevoice_train/data/raw/test.csv 첫 10개</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3046,7 +3050,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v0.1-tmp</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -3056,95 +3060,10 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>카페 주문 도메인. 사용자 보유 — 실제 corpus_id / 통계는 추후 갱신.</t>
+          <t>SenseVoice/Whisper 추론 파이프라인 스모크용 임시 벤치마크 (10 발화)</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
-        <is>
-          <t>TODO: 통계 채우기</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>o</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Sample10_general_clean</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Sample10_PracticeRef</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>clean</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>studio</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>/home/cssong/workspace/practice/2601_sensevoice_train/data/raw/test.csv 첫 10개</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>human-review</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>내부전용</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>v0.1-tmp</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>SenseVoice/Whisper 추론 파이프라인 스모크용 임시 벤치마크 (10 발화)</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
         <is>
           <t>임시 — 본격 운영 시 폐기</t>
         </is>
